--- a/ghg_scen2.xlsx
+++ b/ghg_scen2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7767ba86a98102bc/TEP4290/Project/TEP4290-project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="8_{5885F49E-BCF2-406A-960D-1263DDCCE1AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A241C09C-CEA5-4CAA-9934-AA7ED0ED94E7}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="8_{5885F49E-BCF2-406A-960D-1263DDCCE1AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{674D6369-393A-40BE-95BF-208DF123346D}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="14235" xr2:uid="{350325DE-E4E4-49B1-A932-324630C5E987}"/>
   </bookViews>
@@ -712,7 +712,7 @@
         <f>H12-(0.19*40/100)</f>
         <v>0.11373499999999999</v>
       </c>
-      <c r="L8" t="s">
+      <c r="L8" s="12" t="s">
         <v>50</v>
       </c>
     </row>
@@ -763,7 +763,7 @@
         <f>H18-(1.11*95/100)</f>
         <v>5.0950000000000051E-2</v>
       </c>
-      <c r="L10" t="s">
+      <c r="L10" s="12" t="s">
         <v>46</v>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         <f>10-(10*0.97)</f>
         <v>0.30000000000000071</v>
       </c>
-      <c r="I27" t="s">
+      <c r="I27" s="12" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
       <c r="H28" s="11">
         <v>-0.97</v>
       </c>
-      <c r="I28" t="s">
+      <c r="I28" s="12" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1106,13 +1106,18 @@
       </c>
     </row>
     <row r="30" spans="3:9" x14ac:dyDescent="0.45">
-      <c r="I30" t="s">
+      <c r="I30" s="12" t="s">
         <v>48</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="L12" r:id="rId1" xr:uid="{E69FBC48-5D96-408F-9D0B-57CE3056D5D6}"/>
+    <hyperlink ref="L8" r:id="rId2" xr:uid="{A7AF94AF-4C6E-4187-A687-702D4F5CCCF3}"/>
+    <hyperlink ref="L10" r:id="rId3" xr:uid="{373BC9A1-A69A-454D-B8F5-8BD5AB3A7D06}"/>
+    <hyperlink ref="I28" r:id="rId4" xr:uid="{76BCEE03-E917-40BE-A8A4-4D222CF848A2}"/>
+    <hyperlink ref="I30" r:id="rId5" xr:uid="{2D37E79C-EF1C-46D7-BD0E-08162E04AA3D}"/>
+    <hyperlink ref="I27" r:id="rId6" xr:uid="{5E611D34-4E58-4D24-9482-44A309F8E080}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
